--- a/Data_Online/Data_Figure_4.xlsx
+++ b/Data_Online/Data_Figure_4.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeremycarlot/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jeremycarlot/Documents/Post-Doc – LOV/Projets/Villefranche/Projets/BenthFun – Jeremy (pending)/BenthFun/Data_Online/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B80626D4-D17B-FD45-8504-958AD8CD2EB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{409BC4A5-0D35-AF4B-804D-03D86FD74B9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -91,7 +91,7 @@
     <t>GP</t>
   </si>
   <si>
-    <t>Function</t>
+    <t>Fct</t>
   </si>
 </sst>
 </file>
